--- a/Templates~/Config/Excels/UI/UIWindow.xlsx
+++ b/Templates~/Config/Excels/UI/UIWindow.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Workspace\Unity\Game Dev Tools\Packages\com.moirai.framework\Templates~\Config\Excels\UI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Workspace\Unity\Game Dev Tools\Client\Packages\com.moirai.framework\Templates~\Config\Excels\UI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF98F17-D482-441A-9A84-87B726D42575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0793A79-BF25-4206-9756-4A0777A31102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4635" yWindow="4635" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4980" yWindow="4980" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>##var</t>
   </si>
@@ -84,10 +84,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>hud</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>string#path=unity</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -128,47 +124,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>战斗 HUD</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>设置</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>#obsidian_res</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>credits</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>致谢名单</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>settings</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/AssetRaw/UI/Windows/StartScreen.prefab</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/AssetRaw/UI/Windows/Credits.prefab</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/AssetRaw/UI/Windows/Settings.prefab</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/AssetRaw/UI/Windows/HUD.prefab</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/AssetRaw/UI/Windows/Test.prefab</t>
+    <t>Assets/AssetRaw/Default/UI/Window/Test.prefab</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/AssetRaw/Default/UI/Window/StartScreen.prefab</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -549,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -569,10 +533,10 @@
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -584,10 +548,10 @@
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -611,71 +575,38 @@
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
